--- a/AAII_Financials/Quarterly/ABEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABEV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>ABEV</t>
   </si>
@@ -656,339 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3889200</v>
+      </c>
+      <c r="E8" s="3">
         <v>4306200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4503900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3911700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3687100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3923800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4371200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4058000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3610500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4042700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4119500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4068400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3919400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4054900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4078600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3803800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3605400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3791700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4442700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3724400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3042100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3113100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3631500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3053800</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1872400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2085900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2133700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1898900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1843700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1909100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2024900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2015100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1812100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2005600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1916900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2047000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1998400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2000900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1974400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1967300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1878800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1935900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2118500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1863600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1542300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1486500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1604300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1452700</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2016800</v>
+      </c>
+      <c r="E10" s="3">
         <v>2220300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2370300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2012800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1843400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2014800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2346300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2042900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1798400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2037100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2202700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2021300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1921000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2053900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2104200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1836400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1726600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1855800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2324100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1860800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1499800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1626600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2027200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1601100</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,127 +1180,133 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-5000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>77500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-118500</v>
       </c>
-      <c r="G14" s="3">
-        <v>21100</v>
-      </c>
       <c r="H14" s="3">
+        <v>15700</v>
+      </c>
+      <c r="I14" s="3">
         <v>6800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>45400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>26500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>44400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>109700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-25100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>37700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-53900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-35500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-99600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-84200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-62500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-21000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-34300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-12800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-33700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-9500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>12900</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>295500</v>
+      </c>
+      <c r="E15" s="3">
         <v>246200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>149600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>300100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>312400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>298800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>151800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>317800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>309800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>325500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>119500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>334700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>353400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>301500</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2965800</v>
+      </c>
+      <c r="E17" s="3">
         <v>3176700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3234100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2894200</v>
       </c>
-      <c r="G17" s="3">
-        <v>2893200</v>
-      </c>
       <c r="H17" s="3">
+        <v>2880800</v>
+      </c>
+      <c r="I17" s="3">
         <v>2934800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3158700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3090000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2896800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3074700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2970300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3092500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3187800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3095200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3059600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2951300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2706400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2867700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3362600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2868600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2258700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2321500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2141800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2335700</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>923400</v>
+      </c>
+      <c r="E18" s="3">
         <v>1129500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1269800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1017500</v>
       </c>
-      <c r="G18" s="3">
-        <v>793900</v>
-      </c>
       <c r="H18" s="3">
+        <v>806300</v>
+      </c>
+      <c r="I18" s="3">
         <v>989100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1212500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>968100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>713700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>968000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1149200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>975800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>731600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>959700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1019000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>852400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>898900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>924000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1080000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>855800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>783500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>791700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1489700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>718100</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,378 +1545,394 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E20" s="3">
         <v>164900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>86700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>125700</v>
       </c>
-      <c r="G20" s="3">
-        <v>191000</v>
-      </c>
       <c r="H20" s="3">
+        <v>124500</v>
+      </c>
+      <c r="I20" s="3">
         <v>112800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>52100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>51800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>99600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>44600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-76700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>145900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>173600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>162800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-119200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-206600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-77600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-109000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-162300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-156200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-24300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-183600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>242800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-136800</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1154100</v>
+      </c>
+      <c r="E21" s="3">
         <v>1210800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1332700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1191900</v>
       </c>
-      <c r="G21" s="3">
-        <v>915300</v>
-      </c>
       <c r="H21" s="3">
+        <v>994300</v>
+      </c>
+      <c r="I21" s="3">
         <v>1175100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1312200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1234000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>923900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1248900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1345400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1164600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>911400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1098500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1193200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>927300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1115900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1088700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1212900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>975600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1010900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>844400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1999500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>841000</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>104100</v>
+      </c>
+      <c r="E22" s="3">
         <v>102500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>103900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>91600</v>
       </c>
-      <c r="G22" s="3">
-        <v>75400</v>
-      </c>
       <c r="H22" s="3">
+        <v>92700</v>
+      </c>
+      <c r="I22" s="3">
         <v>88300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>85600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>89500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>47200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>109600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>108100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>126400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>136800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>121800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>122100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>127800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>112200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>81800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>89300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>70700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>58800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>62600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>76100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>105500</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>837600</v>
+      </c>
+      <c r="E23" s="3">
         <v>945300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1076900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>978300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>627600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>847000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1117300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>857600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>618200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>892300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>974100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>812900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>491900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>765800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>777800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>518000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>709200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>733200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>828400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>628900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>700400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>545400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1656500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>475800</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>166900</v>
+      </c>
+      <c r="E24" s="3">
         <v>200500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>254600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>65700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>115500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>183400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>304900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>202600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>176500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>133800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>40800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-46800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-135900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-76000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>95100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>72100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-118900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>133100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>34100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>308000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>670700</v>
+      </c>
+      <c r="E26" s="3">
         <v>744800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>822300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>912600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>512100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>663600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>812400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>654900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>441700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>758500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>933300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>803900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>538800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>754300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>913600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>594000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>614100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>725600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>756300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>747700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>567300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>511400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1348400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>461700</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>653700</v>
+      </c>
+      <c r="E27" s="3">
         <v>722300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>789100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>890400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>498800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>644300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>789100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>635500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>431600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>737800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>904200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>783300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>519100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>730600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>892700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>574300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>595200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>701800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>728100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>715500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>558800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>491200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1328000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>445200</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-64800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-164900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-86700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-125700</v>
       </c>
-      <c r="G32" s="3">
-        <v>-191000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-124500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-112800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-52100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-51800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-99600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-44600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>76700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-145900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-173600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-162800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>119200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>206600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>77600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>109000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>162300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>156200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>24300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>183600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-242800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>136800</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>653700</v>
+      </c>
+      <c r="E33" s="3">
         <v>722300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>789100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>890400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>498800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>644300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>789100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>635500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>431600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>737800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>904200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>783300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>519100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>730600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>892700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>574300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>595200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>701800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>728100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>715500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>558800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>491200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1328000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>445200</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>653700</v>
+      </c>
+      <c r="E35" s="3">
         <v>722300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>789100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>890400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>498800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>644300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>789100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>635500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>431600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>737800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>904200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>783300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>519100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>730600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>892700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>574300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>595200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>701800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>728100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>715500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>558800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>491200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1328000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>445200</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,674 +2917,702 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3206200</v>
+      </c>
+      <c r="E41" s="3">
         <v>3448900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3383800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3435500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3010600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3334500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4623500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3633400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2549600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2561000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3309600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3486900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2513000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2412200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2682700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3272600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2831800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2650100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3356100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3616400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2569300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3234100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3344600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4239000</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>335000</v>
+      </c>
+      <c r="E42" s="3">
         <v>316000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>305300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>287400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>205700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>207900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>200800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>212100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>213800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>214800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>57100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>45500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>65000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>72100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>81700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>248900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>307800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>276700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>386400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>411800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>241200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>383500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>332700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>282400</v>
       </c>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1591800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1692300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1811000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1666000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1619300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1552000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1592900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1571900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1647700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1679100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1891300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1534800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1715500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1599000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1481400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1515800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1604500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1434000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1494500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1316900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1271600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1190600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1485400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1493200</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2010500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1993400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1910000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1964900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2083300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2136200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1890000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2037300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2058100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2133100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1982400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2166300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2500200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2573500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2322700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2308600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2522800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2349600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2220300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1915600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1855600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1814400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1488500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1436800</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>668900</v>
+      </c>
+      <c r="E45" s="3">
         <v>760200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>555700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>515800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>567500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>365300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>448900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>382200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>286200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>325600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>294900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>285900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>324900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>330200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>228300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>332200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>396900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>379600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>339100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>432300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>395000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>311000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>265400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>200400</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7812400</v>
+      </c>
+      <c r="E46" s="3">
         <v>8210800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7965800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7869600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7486400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7595900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8756100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7836800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6901900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6913600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7535200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7519400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7118700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6987000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6796800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7678100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7663800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7090100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7796500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7692900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6332800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6933500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6916500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7651600</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>223100</v>
+      </c>
+      <c r="E47" s="3">
         <v>224100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>110600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>83500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>84900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>96900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>93800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>105800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>103800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>107800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>109500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>110800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>119500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>116300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2232300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2011600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2273200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2649600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2707600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2498900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2414200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2094900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2205400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1048400</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4949900</v>
+      </c>
+      <c r="E48" s="3">
         <v>5058300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5018900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4953400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5043100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4968600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4878000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5283100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5227200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5508100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5488200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5791900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6073500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5883400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5401900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5529300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5889700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5653700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5898600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5484500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4976700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4991000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4847200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4977800</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9777300</v>
+      </c>
+      <c r="E49" s="3">
         <v>9943000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9546300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9627300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9733900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9465000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9195500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9815200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9674700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9982700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9901600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9858500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10050700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9763000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8953500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9387300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9997200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9649300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10314100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10046900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9194900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9536000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9316100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9662700</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,82 +3762,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2293200</v>
+      </c>
+      <c r="E52" s="3">
         <v>2324600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2173700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2162100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2111200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2126600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1946200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2329700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2333600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2532300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2659500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2486200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2608700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2579300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1410700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1641500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1560200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1154600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1258700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1492600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1176800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1405800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1215800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1524500</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26677200</v>
+      </c>
+      <c r="E54" s="3">
         <v>27366000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26341200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26411000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>26089700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25690900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26275000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27048800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25837400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26680700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27336300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27615400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27644700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26753600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>24795200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26247700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>27384100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26197200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>27975500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>27215800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>24095300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>24961100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>24501000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>24865000</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,452 +4053,471 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4000400</v>
+      </c>
+      <c r="E57" s="3">
         <v>4256800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4310600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3626100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3649100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3940200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4078200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3869800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3739400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4356200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4780200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3648800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3853400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4270400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4372600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3937800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4245200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4514600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5061700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3701600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3460700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3636500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3558200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2940000</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>207200</v>
+      </c>
+      <c r="E58" s="3">
         <v>211700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>211900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>197100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>202000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>195400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>206400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>222400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>224200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>328300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>267500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>247700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>295400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>255800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>176600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>140700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>179200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>167800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>171000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>179100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>165500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>486200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>536000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>845100</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2279100</v>
+      </c>
+      <c r="E59" s="3">
         <v>2365400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2266800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1857900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1873400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1636500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2338100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1243700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1198800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1172700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1678900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1576700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1753000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1479700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2737200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2384300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2369300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2140300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2612100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2384400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1948700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1841800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2457400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2139800</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7647800</v>
+      </c>
+      <c r="E60" s="3">
         <v>7986700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8278700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6863300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6767000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6862000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7985400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6551300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6235700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6960800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8450600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6777200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7076700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7037100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7286400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6462900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6793800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6822600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7844800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6265000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5574900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5964600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6551600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5924900</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E61" s="3">
         <v>383700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>403000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>346300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>377500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>365800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>351900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>398400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>398300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>432800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>454000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>497000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>554100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>523600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>501100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>410000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>461300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>446300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>454800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>430700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>413600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>454300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>401900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>496500</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>426200</v>
+      </c>
+      <c r="E62" s="3">
         <v>451500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>466300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>685200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>694000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>670600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>665800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>701900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>689900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>721700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>816600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>814100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>918100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>974500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2031200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2459900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2574800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2437500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2717800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2763700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2596800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2895900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2840400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2871000</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9519000</v>
+      </c>
+      <c r="E66" s="3">
         <v>9955900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10223700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9011600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8983000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9038600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10174400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8889000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8538700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9259300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10819700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9281600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9732800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9683000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10065300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9586400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10095200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9968300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11294900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9740100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8819900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9611500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10055300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9599200</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11918300</v>
+      </c>
+      <c r="E72" s="3">
         <v>11220400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9844200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11365300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10546400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9790600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8672300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10656100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9685700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9913800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8900900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10147500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9465400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8270200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7126400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8526300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8396200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7781900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6670000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7711900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6612500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5748100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5377600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5479700</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17046200</v>
+      </c>
+      <c r="E76" s="3">
         <v>17276300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15961200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17267900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16971000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16487000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15948900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18023300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17159500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17265300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16274600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18072300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17644100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16786700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14729900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16661300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17288900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16229000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16680700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17475700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15275400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15349600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14445700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15265800</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>653700</v>
+      </c>
+      <c r="E81" s="3">
         <v>722300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>789100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>890400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>498800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>644300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>789100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>635500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>431600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>737800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>904200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>783300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>519100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>730600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>892700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>574300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>595200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>701800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>728100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>715500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>558800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>491200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1328000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>445200</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,82 +5810,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>312400</v>
+      </c>
+      <c r="E83" s="3">
         <v>298800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>193500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>317800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>309800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>325500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>170900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>334700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>353400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>301500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>213700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>281500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>280900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>280000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>293400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>281500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>294500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>273700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>295200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>276000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>251700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>236400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>267000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>259700</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>909400</v>
+      </c>
+      <c r="E89" s="3">
         <v>605900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2405900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1298300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>559800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>210000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2249700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1489100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>604900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>143200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2874700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1586500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>708400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-113800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2122800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1128800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>441400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>106900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2386900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1288600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>356400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>530700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1642600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1385400</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,82 +6378,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-169800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-89500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-296000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-195900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-199700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-144400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-245600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-217800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-185200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-202600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-468400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-256800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-268700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-227700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2035500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1855900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1753100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-888500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3010300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1699700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-317500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-248300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-272900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-224000</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-164300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-463400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-369400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-219500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-176400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-136800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-237800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-208300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-194400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-354800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-465100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-242300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-252700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-213400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-196900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-304700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-391300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-63200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-541000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-498800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-165600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-322300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-322900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-521300</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,82 +6715,86 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>228300</v>
+      </c>
+      <c r="E96" s="3">
         <v>300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1759200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>390600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>381800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1153100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>625500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>16500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>15500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>2300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>2396800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>25100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>26700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>7500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2149500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-21700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-28600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-4500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1941200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-5000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-44900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-232200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1305100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-25400</v>
       </c>
     </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,226 +7021,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-862600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-230900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1949200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-604800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-726700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1539500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-850900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-199800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-306100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-459000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2471000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-280700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-353900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-200700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2279000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-171200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-559200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2124200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>31200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-754200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-332600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1874600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-168600</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-154800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-186600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>263600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-47100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>131500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>29700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-217500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>17700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-110900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-24000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-86400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>23900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>110100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-272200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-82100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>23900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>115400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-266000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>46700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>99200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-232600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>160800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-206600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>133000</v>
       </c>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-266600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-123900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>60000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>357200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-498200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1653000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1424600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1033900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>236000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-640900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-278900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1081200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-552000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-435300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>676800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>163200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-781500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-231600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>920300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-796000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>36600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-761500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>828500</v>
       </c>
     </row>
